--- a/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T07:52:36+00:00</t>
+    <t>2024-07-17T09:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T09:13:15+00:00</t>
+    <t>2024-07-17T12:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -401,7 +401,7 @@
     <t>DataTrace : Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI).</t>
   </si>
   <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source.</t>
   </si>
   <si>
     <t>PractitionerRole.meta.versionId</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3000" uniqueCount="505">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:12:47+00:00</t>
+    <t>2024-07-17T15:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -490,7 +490,7 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role-exercice</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role</t>
   </si>
   <si>
     <t>PractitionerRole.meta.security</t>
@@ -865,11 +865,10 @@
     <t>PractitionerRole.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value | Namespace du RASS)</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.
-Namespace du RASS)</t>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>Identifier.system is always case sensitive.</t>
@@ -942,7 +941,15 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
     <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>CX.7 + CX.8</t>
@@ -974,6 +981,10 @@
   </si>
   <si>
     <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
@@ -5194,7 +5205,7 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>119</v>
@@ -5206,7 +5217,7 @@
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5313,7 +5324,7 @@
         <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>102</v>
@@ -5432,7 +5443,7 @@
         <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>102</v>
@@ -5551,7 +5562,7 @@
         <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>102</v>
@@ -5668,7 +5679,7 @@
         <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>102</v>
@@ -5725,7 +5736,9 @@
       <c r="M33" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="N33" s="2"/>
+      <c r="N33" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5774,7 +5787,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5783,22 +5796,22 @@
         <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>299</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
@@ -5806,10 +5819,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5832,16 +5845,16 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5891,7 +5904,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5900,22 +5913,22 @@
         <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>78</v>
@@ -5923,13 +5936,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>230</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>78</v>
@@ -5954,7 +5967,7 @@
         <v>231</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M35" t="s" s="2">
         <v>233</v>
@@ -6025,7 +6038,7 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>237</v>
@@ -6042,7 +6055,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>245</v>
@@ -6157,7 +6170,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>247</v>
@@ -6251,7 +6264,7 @@
         <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>119</v>
@@ -6263,7 +6276,7 @@
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6274,7 +6287,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>249</v>
@@ -6370,7 +6383,7 @@
         <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>102</v>
@@ -6393,7 +6406,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>260</v>
@@ -6489,7 +6502,7 @@
         <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>102</v>
@@ -6512,7 +6525,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>271</v>
@@ -6560,7 +6573,7 @@
         <v>78</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>277</v>
@@ -6608,7 +6621,7 @@
         <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>102</v>
@@ -6631,7 +6644,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>283</v>
@@ -6725,7 +6738,7 @@
         <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>102</v>
@@ -6748,7 +6761,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>293</v>
@@ -6782,7 +6795,9 @@
       <c r="M42" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="N42" s="2"/>
+      <c r="N42" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6831,7 +6846,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6840,22 +6855,22 @@
         <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>299</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
@@ -6863,10 +6878,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6889,16 +6904,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6948,7 +6963,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6957,22 +6972,22 @@
         <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>78</v>
@@ -6980,10 +6995,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7006,70 +7021,70 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="M44" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q44" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="R44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="P44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q44" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="R44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7087,24 +7102,24 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7130,14 +7145,14 @@
         <v>294</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7186,7 +7201,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7204,24 +7219,24 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7333,10 +7348,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7450,10 +7465,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7476,16 +7491,16 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7535,7 +7550,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7544,19 +7559,19 @@
         <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7567,10 +7582,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7593,23 +7608,23 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q49" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="R49" t="s" s="2">
         <v>78</v>
@@ -7654,7 +7669,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7663,19 +7678,19 @@
         <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7686,10 +7701,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7712,13 +7727,13 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7769,7 +7784,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7790,7 +7805,7 @@
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7801,10 +7816,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7827,13 +7842,13 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7884,7 +7899,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7905,7 +7920,7 @@
         <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7916,10 +7931,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7945,16 +7960,16 @@
         <v>261</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7983,13 +7998,13 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
@@ -7999,7 +8014,7 @@
         <v>117</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8017,13 +8032,13 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>78</v>
@@ -8031,13 +8046,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>78</v>
@@ -8062,16 +8077,16 @@
         <v>261</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8100,7 +8115,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8118,7 +8133,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8133,16 +8148,16 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
@@ -8150,13 +8165,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>78</v>
@@ -8181,16 +8196,16 @@
         <v>261</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8219,7 +8234,7 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8237,7 +8252,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8252,16 +8267,16 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8269,13 +8284,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>78</v>
@@ -8300,16 +8315,16 @@
         <v>261</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8338,7 +8353,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -8356,7 +8371,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8371,16 +8386,16 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8388,13 +8403,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>78</v>
@@ -8419,16 +8434,16 @@
         <v>261</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8457,7 +8472,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8475,7 +8490,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8490,16 +8505,16 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
@@ -8507,13 +8522,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>78</v>
@@ -8538,16 +8553,16 @@
         <v>261</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8576,7 +8591,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8594,7 +8609,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8609,16 +8624,16 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -8626,13 +8641,13 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>78</v>
@@ -8657,16 +8672,16 @@
         <v>261</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8695,7 +8710,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8713,7 +8728,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8728,16 +8743,16 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>78</v>
@@ -8745,13 +8760,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
@@ -8776,16 +8791,16 @@
         <v>261</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8814,7 +8829,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -8832,7 +8847,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8847,16 +8862,16 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
@@ -8864,10 +8879,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8893,10 +8908,10 @@
         <v>261</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8927,25 +8942,25 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8963,13 +8978,13 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -8977,10 +8992,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9003,13 +9018,13 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9060,7 +9075,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9081,21 +9096,21 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9118,13 +9133,13 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9175,7 +9190,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9193,10 +9208,10 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9207,10 +9222,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9233,17 +9248,17 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9280,7 +9295,7 @@
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
@@ -9290,7 +9305,7 @@
         <v>117</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9302,19 +9317,19 @@
         <v>209</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9322,13 +9337,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>78</v>
@@ -9350,17 +9365,17 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9409,7 +9424,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9421,19 +9436,19 @@
         <v>209</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -9441,10 +9456,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9467,16 +9482,16 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9526,7 +9541,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9547,7 +9562,7 @@
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9558,10 +9573,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9673,10 +9688,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9790,14 +9805,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9819,10 +9834,10 @@
         <v>111</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>114</v>
@@ -9877,7 +9892,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9909,10 +9924,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9938,10 +9953,10 @@
         <v>176</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9971,28 +9986,28 @@
         <v>254</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10013,7 +10028,7 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
@@ -10024,10 +10039,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10050,13 +10065,13 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10107,7 +10122,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10128,7 +10143,7 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -10139,10 +10154,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10165,16 +10180,16 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10224,7 +10239,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10245,7 +10260,7 @@
         <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10256,10 +10271,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10282,16 +10297,16 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="M72" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10341,7 +10356,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10362,7 +10377,7 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10373,10 +10388,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10399,13 +10414,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10456,7 +10471,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10477,7 +10492,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10488,10 +10503,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10603,10 +10618,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10720,14 +10735,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10749,10 +10764,10 @@
         <v>111</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>114</v>
@@ -10807,7 +10822,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10839,10 +10854,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10868,10 +10883,10 @@
         <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10922,7 +10937,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>90</v>
@@ -10954,10 +10969,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10983,10 +10998,10 @@
         <v>294</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11037,7 +11052,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11058,7 +11073,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -11069,10 +11084,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11098,10 +11113,10 @@
         <v>104</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11152,7 +11167,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11173,7 +11188,7 @@
         <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11184,10 +11199,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11210,17 +11225,17 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -11269,7 +11284,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:12:21+00:00</t>
+    <t>2024-07-25T07:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
